--- a/Bibsam_tidskriftslistor/scifree_data_pensoft.xlsx
+++ b/Bibsam_tidskriftslistor/scifree_data_pensoft.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\larher\Documents\GitHub\oa-tskr\Bibsam_tidskriftslistor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7323FCAD-AD93-4429-BB0E-6DB28FEB2701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8EC7452-5899-4262-B196-277EC4B6EF39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E595E490-612E-4D43-91C0-BB7A78A3E21F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="253">
   <si>
     <t>Imprint</t>
   </si>
@@ -768,6 +768,108 @@
   </si>
   <si>
     <t>CC-BY</t>
+  </si>
+  <si>
+    <t>3033-2117</t>
+  </si>
+  <si>
+    <t>Advances in Pollinator Research</t>
+  </si>
+  <si>
+    <t>https://apr.pensoft.net/</t>
+  </si>
+  <si>
+    <t>3061-0214</t>
+  </si>
+  <si>
+    <t>3061-0206</t>
+  </si>
+  <si>
+    <t>The Annals of the Natural History Museum Vienna</t>
+  </si>
+  <si>
+    <t>https://anhmw.pensoft.net/</t>
+  </si>
+  <si>
+    <t>2710-298X</t>
+  </si>
+  <si>
+    <t>1026-4949</t>
+  </si>
+  <si>
+    <t>Biosystematics and Ecology</t>
+  </si>
+  <si>
+    <t>https://biosystecol.oeaw.ac.at/</t>
+  </si>
+  <si>
+    <t>2667-9809</t>
+  </si>
+  <si>
+    <t>Caucasiana</t>
+  </si>
+  <si>
+    <t>https://caucasiana.pensoft.net/</t>
+  </si>
+  <si>
+    <t>1314-0027</t>
+  </si>
+  <si>
+    <t>1310-7771</t>
+  </si>
+  <si>
+    <t>Phytologia Balcanica</t>
+  </si>
+  <si>
+    <t>https://phytolbalcan.arphahub.com/</t>
+  </si>
+  <si>
+    <t>2367-8518</t>
+  </si>
+  <si>
+    <t>2367-850X</t>
+  </si>
+  <si>
+    <t>Problems of Dental Medicine</t>
+  </si>
+  <si>
+    <t>https://pdm.pensoft.net/</t>
+  </si>
+  <si>
+    <t>2247-9902</t>
+  </si>
+  <si>
+    <t>1842-614X</t>
+  </si>
+  <si>
+    <t>The Scientific Annals of the Danube Delta Institute</t>
+  </si>
+  <si>
+    <t>https://saddi.pensoft.net/</t>
+  </si>
+  <si>
+    <t>1661-8734</t>
+  </si>
+  <si>
+    <t>1661-8726</t>
+  </si>
+  <si>
+    <t>Swiss Journal of Geosciences</t>
+  </si>
+  <si>
+    <t>https://sjg.pensoft.net/</t>
+  </si>
+  <si>
+    <t>1664-2384</t>
+  </si>
+  <si>
+    <t>1664-2376</t>
+  </si>
+  <si>
+    <t>Swiss Journal of Palaeontology</t>
+  </si>
+  <si>
+    <t>https://sjp.pensoft.net/</t>
   </si>
 </sst>
 </file>
@@ -823,8 +925,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{604384D0-4DBF-44C9-9DDF-E867BE9A15D4}" name="Table1" displayName="Table1" ref="A1:G58" totalsRowShown="0">
-  <autoFilter ref="A1:G58" xr:uid="{604384D0-4DBF-44C9-9DDF-E867BE9A15D4}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{604384D0-4DBF-44C9-9DDF-E867BE9A15D4}" name="Table1" displayName="Table1" ref="A1:G67" totalsRowShown="0">
+  <autoFilter ref="A1:G67" xr:uid="{604384D0-4DBF-44C9-9DDF-E867BE9A15D4}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G67">
+    <sortCondition ref="D1:D67"/>
+  </sortState>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{81B5F50D-C4B2-4F16-9B13-3D64AF546E5B}" name="Imprint"/>
     <tableColumn id="2" xr3:uid="{43CA14FF-68A9-421B-9C63-4C8FA72DAE05}" name="ISSN Electronic"/>
@@ -1155,7 +1260,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{292E5242-1A03-4939-89CC-D708A2B4075E}">
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5703125" customWidth="1"/>
@@ -1218,16 +1323,13 @@
         <v>158</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C3" t="s">
-        <v>66</v>
+        <v>219</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>220</v>
       </c>
       <c r="E3" t="s">
-        <v>161</v>
+        <v>221</v>
       </c>
       <c r="F3" t="s">
         <v>217</v>
@@ -1241,16 +1343,16 @@
         <v>158</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F4" t="s">
         <v>217</v>
@@ -1264,16 +1366,16 @@
         <v>158</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F5" t="s">
         <v>217</v>
@@ -1287,13 +1389,16 @@
         <v>158</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>69</v>
+      </c>
+      <c r="C6" t="s">
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F6" t="s">
         <v>217</v>
@@ -1307,16 +1412,13 @@
         <v>158</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F7" t="s">
         <v>217</v>
@@ -1330,16 +1432,16 @@
         <v>158</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F8" t="s">
         <v>217</v>
@@ -1353,16 +1455,16 @@
         <v>158</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>226</v>
       </c>
       <c r="C9" t="s">
-        <v>77</v>
+        <v>227</v>
       </c>
       <c r="D9" t="s">
-        <v>14</v>
+        <v>228</v>
       </c>
       <c r="E9" t="s">
-        <v>167</v>
+        <v>229</v>
       </c>
       <c r="F9" t="s">
         <v>217</v>
@@ -1376,16 +1478,16 @@
         <v>158</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D10" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E10" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F10" t="s">
         <v>217</v>
@@ -1399,13 +1501,16 @@
         <v>158</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>76</v>
+      </c>
+      <c r="C11" t="s">
+        <v>77</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E11" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F11" t="s">
         <v>217</v>
@@ -1419,16 +1524,16 @@
         <v>158</v>
       </c>
       <c r="B12" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C12" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E12" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F12" t="s">
         <v>217</v>
@@ -1442,16 +1547,13 @@
         <v>158</v>
       </c>
       <c r="B13" t="s">
-        <v>83</v>
-      </c>
-      <c r="C13" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
+        <v>231</v>
       </c>
       <c r="E13" t="s">
-        <v>171</v>
+        <v>232</v>
       </c>
       <c r="F13" t="s">
         <v>217</v>
@@ -1465,16 +1567,13 @@
         <v>158</v>
       </c>
       <c r="B14" t="s">
-        <v>85</v>
-      </c>
-      <c r="C14" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D14" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E14" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F14" t="s">
         <v>217</v>
@@ -1488,13 +1587,16 @@
         <v>158</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>81</v>
+      </c>
+      <c r="C15" t="s">
+        <v>82</v>
       </c>
       <c r="D15" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E15" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F15" t="s">
         <v>217</v>
@@ -1508,16 +1610,16 @@
         <v>158</v>
       </c>
       <c r="B16" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C16" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D16" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E16" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F16" t="s">
         <v>217</v>
@@ -1531,13 +1633,16 @@
         <v>158</v>
       </c>
       <c r="B17" t="s">
-        <v>90</v>
+        <v>85</v>
+      </c>
+      <c r="C17" t="s">
+        <v>86</v>
       </c>
       <c r="D17" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E17" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F17" t="s">
         <v>217</v>
@@ -1551,16 +1656,13 @@
         <v>158</v>
       </c>
       <c r="B18" t="s">
-        <v>91</v>
-      </c>
-      <c r="C18" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D18" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E18" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F18" t="s">
         <v>217</v>
@@ -1574,13 +1676,16 @@
         <v>158</v>
       </c>
       <c r="B19" t="s">
-        <v>93</v>
+        <v>88</v>
+      </c>
+      <c r="C19" t="s">
+        <v>89</v>
       </c>
       <c r="D19" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E19" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F19" t="s">
         <v>217</v>
@@ -1594,16 +1699,13 @@
         <v>158</v>
       </c>
       <c r="B20" t="s">
-        <v>94</v>
-      </c>
-      <c r="C20" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D20" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E20" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F20" t="s">
         <v>217</v>
@@ -1617,13 +1719,16 @@
         <v>158</v>
       </c>
       <c r="B21" t="s">
-        <v>96</v>
+        <v>91</v>
+      </c>
+      <c r="C21" t="s">
+        <v>92</v>
       </c>
       <c r="D21" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E21" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F21" t="s">
         <v>217</v>
@@ -1637,16 +1742,13 @@
         <v>158</v>
       </c>
       <c r="B22" t="s">
-        <v>97</v>
-      </c>
-      <c r="C22" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D22" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E22" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F22" t="s">
         <v>217</v>
@@ -1660,13 +1762,16 @@
         <v>158</v>
       </c>
       <c r="B23" t="s">
-        <v>99</v>
+        <v>94</v>
+      </c>
+      <c r="C23" t="s">
+        <v>95</v>
       </c>
       <c r="D23" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E23" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F23" t="s">
         <v>217</v>
@@ -1680,16 +1785,13 @@
         <v>158</v>
       </c>
       <c r="B24" t="s">
-        <v>100</v>
-      </c>
-      <c r="C24" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D24" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E24" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F24" t="s">
         <v>217</v>
@@ -1703,16 +1805,16 @@
         <v>158</v>
       </c>
       <c r="B25" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C25" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D25" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E25" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F25" t="s">
         <v>217</v>
@@ -1726,13 +1828,13 @@
         <v>158</v>
       </c>
       <c r="B26" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D26" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E26" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F26" t="s">
         <v>217</v>
@@ -1746,13 +1848,16 @@
         <v>158</v>
       </c>
       <c r="B27" t="s">
-        <v>105</v>
+        <v>100</v>
+      </c>
+      <c r="C27" t="s">
+        <v>101</v>
       </c>
       <c r="D27" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E27" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F27" t="s">
         <v>217</v>
@@ -1766,13 +1871,16 @@
         <v>158</v>
       </c>
       <c r="B28" t="s">
-        <v>106</v>
+        <v>102</v>
+      </c>
+      <c r="C28" t="s">
+        <v>103</v>
       </c>
       <c r="D28" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E28" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F28" t="s">
         <v>217</v>
@@ -1786,16 +1894,13 @@
         <v>158</v>
       </c>
       <c r="B29" t="s">
-        <v>107</v>
-      </c>
-      <c r="C29" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D29" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E29" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F29" t="s">
         <v>217</v>
@@ -1809,16 +1914,13 @@
         <v>158</v>
       </c>
       <c r="B30" t="s">
-        <v>109</v>
-      </c>
-      <c r="C30" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D30" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E30" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F30" t="s">
         <v>217</v>
@@ -1832,16 +1934,13 @@
         <v>158</v>
       </c>
       <c r="B31" t="s">
-        <v>111</v>
-      </c>
-      <c r="C31" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D31" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E31" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F31" t="s">
         <v>217</v>
@@ -1855,16 +1954,16 @@
         <v>158</v>
       </c>
       <c r="B32" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C32" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D32" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E32" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="F32" t="s">
         <v>217</v>
@@ -1878,16 +1977,16 @@
         <v>158</v>
       </c>
       <c r="B33" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C33" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D33" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E33" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F33" t="s">
         <v>217</v>
@@ -1901,16 +2000,16 @@
         <v>158</v>
       </c>
       <c r="B34" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C34" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D34" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E34" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F34" t="s">
         <v>217</v>
@@ -1924,13 +2023,16 @@
         <v>158</v>
       </c>
       <c r="B35" t="s">
-        <v>119</v>
+        <v>113</v>
+      </c>
+      <c r="C35" t="s">
+        <v>114</v>
       </c>
       <c r="D35" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E35" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F35" t="s">
         <v>217</v>
@@ -1944,16 +2046,16 @@
         <v>158</v>
       </c>
       <c r="B36" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C36" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D36" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E36" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F36" t="s">
         <v>217</v>
@@ -1967,13 +2069,16 @@
         <v>158</v>
       </c>
       <c r="B37" t="s">
-        <v>122</v>
+        <v>117</v>
+      </c>
+      <c r="C37" t="s">
+        <v>118</v>
       </c>
       <c r="D37" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E37" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F37" t="s">
         <v>217</v>
@@ -1987,16 +2092,13 @@
         <v>158</v>
       </c>
       <c r="B38" t="s">
-        <v>123</v>
-      </c>
-      <c r="C38" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D38" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E38" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F38" t="s">
         <v>217</v>
@@ -2010,16 +2112,16 @@
         <v>158</v>
       </c>
       <c r="B39" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C39" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D39" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E39" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F39" t="s">
         <v>217</v>
@@ -2033,13 +2135,13 @@
         <v>158</v>
       </c>
       <c r="B40" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D40" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E40" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F40" t="s">
         <v>217</v>
@@ -2053,16 +2155,16 @@
         <v>158</v>
       </c>
       <c r="B41" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C41" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D41" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E41" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F41" t="s">
         <v>217</v>
@@ -2076,13 +2178,16 @@
         <v>158</v>
       </c>
       <c r="B42" t="s">
-        <v>130</v>
+        <v>125</v>
+      </c>
+      <c r="C42" t="s">
+        <v>126</v>
       </c>
       <c r="D42" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E42" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F42" t="s">
         <v>217</v>
@@ -2096,13 +2201,13 @@
         <v>158</v>
       </c>
       <c r="B43" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D43" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E43" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F43" t="s">
         <v>217</v>
@@ -2116,16 +2221,16 @@
         <v>158</v>
       </c>
       <c r="B44" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C44" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D44" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E44" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F44" t="s">
         <v>217</v>
@@ -2139,16 +2244,13 @@
         <v>158</v>
       </c>
       <c r="B45" t="s">
-        <v>134</v>
-      </c>
-      <c r="C45" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="D45" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E45" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F45" t="s">
         <v>217</v>
@@ -2162,16 +2264,13 @@
         <v>158</v>
       </c>
       <c r="B46" t="s">
-        <v>136</v>
-      </c>
-      <c r="C46" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D46" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E46" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F46" t="s">
         <v>217</v>
@@ -2185,13 +2284,16 @@
         <v>158</v>
       </c>
       <c r="B47" t="s">
-        <v>138</v>
+        <v>132</v>
+      </c>
+      <c r="C47" t="s">
+        <v>133</v>
       </c>
       <c r="D47" t="s">
-        <v>159</v>
+        <v>49</v>
       </c>
       <c r="E47" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F47" t="s">
         <v>217</v>
@@ -2205,13 +2307,16 @@
         <v>158</v>
       </c>
       <c r="B48" t="s">
-        <v>139</v>
+        <v>134</v>
+      </c>
+      <c r="C48" t="s">
+        <v>135</v>
       </c>
       <c r="D48" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E48" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F48" t="s">
         <v>217</v>
@@ -2225,16 +2330,16 @@
         <v>158</v>
       </c>
       <c r="B49" t="s">
-        <v>140</v>
+        <v>233</v>
       </c>
       <c r="C49" t="s">
-        <v>141</v>
+        <v>234</v>
       </c>
       <c r="D49" t="s">
-        <v>53</v>
+        <v>235</v>
       </c>
       <c r="E49" t="s">
-        <v>207</v>
+        <v>236</v>
       </c>
       <c r="F49" t="s">
         <v>217</v>
@@ -2248,16 +2353,16 @@
         <v>158</v>
       </c>
       <c r="B50" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C50" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="D50" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E50" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="F50" t="s">
         <v>217</v>
@@ -2271,16 +2376,16 @@
         <v>158</v>
       </c>
       <c r="B51" t="s">
-        <v>144</v>
+        <v>237</v>
       </c>
       <c r="C51" t="s">
-        <v>145</v>
+        <v>238</v>
       </c>
       <c r="D51" t="s">
-        <v>55</v>
+        <v>239</v>
       </c>
       <c r="E51" t="s">
-        <v>209</v>
+        <v>240</v>
       </c>
       <c r="F51" t="s">
         <v>217</v>
@@ -2294,16 +2399,13 @@
         <v>158</v>
       </c>
       <c r="B52" t="s">
-        <v>146</v>
-      </c>
-      <c r="C52" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="D52" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E52" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="F52" t="s">
         <v>217</v>
@@ -2317,13 +2419,16 @@
         <v>158</v>
       </c>
       <c r="B53" t="s">
-        <v>148</v>
+        <v>140</v>
+      </c>
+      <c r="C53" t="s">
+        <v>141</v>
       </c>
       <c r="D53" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E53" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="F53" t="s">
         <v>217</v>
@@ -2337,16 +2442,16 @@
         <v>158</v>
       </c>
       <c r="B54" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="C54" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="D54" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E54" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="F54" t="s">
         <v>217</v>
@@ -2360,13 +2465,16 @@
         <v>158</v>
       </c>
       <c r="B55" t="s">
-        <v>151</v>
+        <v>245</v>
+      </c>
+      <c r="C55" t="s">
+        <v>246</v>
       </c>
       <c r="D55" t="s">
-        <v>59</v>
+        <v>247</v>
       </c>
       <c r="E55" t="s">
-        <v>213</v>
+        <v>248</v>
       </c>
       <c r="F55" t="s">
         <v>217</v>
@@ -2380,16 +2488,16 @@
         <v>158</v>
       </c>
       <c r="B56" t="s">
-        <v>152</v>
+        <v>249</v>
       </c>
       <c r="C56" t="s">
-        <v>153</v>
+        <v>250</v>
       </c>
       <c r="D56" t="s">
-        <v>60</v>
+        <v>251</v>
       </c>
       <c r="E56" t="s">
-        <v>214</v>
+        <v>252</v>
       </c>
       <c r="F56" t="s">
         <v>217</v>
@@ -2403,16 +2511,16 @@
         <v>158</v>
       </c>
       <c r="B57" t="s">
-        <v>154</v>
+        <v>222</v>
       </c>
       <c r="C57" t="s">
-        <v>155</v>
+        <v>223</v>
       </c>
       <c r="D57" t="s">
-        <v>61</v>
+        <v>224</v>
       </c>
       <c r="E57" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="F57" t="s">
         <v>217</v>
@@ -2426,21 +2534,219 @@
         <v>158</v>
       </c>
       <c r="B58" t="s">
+        <v>241</v>
+      </c>
+      <c r="C58" t="s">
+        <v>242</v>
+      </c>
+      <c r="D58" t="s">
+        <v>243</v>
+      </c>
+      <c r="E58" t="s">
+        <v>244</v>
+      </c>
+      <c r="F58" t="s">
+        <v>217</v>
+      </c>
+      <c r="G58" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>158</v>
+      </c>
+      <c r="B59" t="s">
+        <v>144</v>
+      </c>
+      <c r="C59" t="s">
+        <v>145</v>
+      </c>
+      <c r="D59" t="s">
+        <v>55</v>
+      </c>
+      <c r="E59" t="s">
+        <v>209</v>
+      </c>
+      <c r="F59" t="s">
+        <v>217</v>
+      </c>
+      <c r="G59" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>158</v>
+      </c>
+      <c r="B60" t="s">
+        <v>146</v>
+      </c>
+      <c r="C60" t="s">
+        <v>147</v>
+      </c>
+      <c r="D60" t="s">
+        <v>56</v>
+      </c>
+      <c r="E60" t="s">
+        <v>210</v>
+      </c>
+      <c r="F60" t="s">
+        <v>217</v>
+      </c>
+      <c r="G60" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>158</v>
+      </c>
+      <c r="B61" t="s">
+        <v>148</v>
+      </c>
+      <c r="D61" t="s">
+        <v>57</v>
+      </c>
+      <c r="E61" t="s">
+        <v>211</v>
+      </c>
+      <c r="F61" t="s">
+        <v>217</v>
+      </c>
+      <c r="G61" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>158</v>
+      </c>
+      <c r="B62" t="s">
+        <v>138</v>
+      </c>
+      <c r="D62" t="s">
+        <v>159</v>
+      </c>
+      <c r="E62" t="s">
+        <v>205</v>
+      </c>
+      <c r="F62" t="s">
+        <v>217</v>
+      </c>
+      <c r="G62" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>158</v>
+      </c>
+      <c r="B63" t="s">
+        <v>149</v>
+      </c>
+      <c r="C63" t="s">
+        <v>150</v>
+      </c>
+      <c r="D63" t="s">
+        <v>58</v>
+      </c>
+      <c r="E63" t="s">
+        <v>212</v>
+      </c>
+      <c r="F63" t="s">
+        <v>217</v>
+      </c>
+      <c r="G63" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>158</v>
+      </c>
+      <c r="B64" t="s">
+        <v>151</v>
+      </c>
+      <c r="D64" t="s">
+        <v>59</v>
+      </c>
+      <c r="E64" t="s">
+        <v>213</v>
+      </c>
+      <c r="F64" t="s">
+        <v>217</v>
+      </c>
+      <c r="G64" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>158</v>
+      </c>
+      <c r="B65" t="s">
+        <v>152</v>
+      </c>
+      <c r="C65" t="s">
+        <v>153</v>
+      </c>
+      <c r="D65" t="s">
+        <v>60</v>
+      </c>
+      <c r="E65" t="s">
+        <v>214</v>
+      </c>
+      <c r="F65" t="s">
+        <v>217</v>
+      </c>
+      <c r="G65" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>158</v>
+      </c>
+      <c r="B66" t="s">
+        <v>154</v>
+      </c>
+      <c r="C66" t="s">
+        <v>155</v>
+      </c>
+      <c r="D66" t="s">
+        <v>61</v>
+      </c>
+      <c r="E66" t="s">
+        <v>215</v>
+      </c>
+      <c r="F66" t="s">
+        <v>217</v>
+      </c>
+      <c r="G66" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>158</v>
+      </c>
+      <c r="B67" t="s">
         <v>156</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C67" t="s">
         <v>157</v>
       </c>
-      <c r="D58" t="s">
+      <c r="D67" t="s">
         <v>62</v>
       </c>
-      <c r="E58" t="s">
+      <c r="E67" t="s">
         <v>216</v>
       </c>
-      <c r="F58" t="s">
-        <v>217</v>
-      </c>
-      <c r="G58" t="s">
+      <c r="F67" t="s">
+        <v>217</v>
+      </c>
+      <c r="G67" t="s">
         <v>218</v>
       </c>
     </row>
